--- a/data_extactor/batch_10_fa/batch_0007_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0007_fa.xlsx
@@ -498,37 +498,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Buyer | Grain Buyer | Grain Merchandiser | Grain Origination Specialist | Purchasing Agent | Tobacco Buyer</t>
+          <t>خریدار | خریدار غلات | بازرگان غلات | کارشناس تأمین غلات | کارگزار خرید | خریدار توتون</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار Amazon Web Services AWS | Atlassian JIRA | Deltek Costpoint | سیستم ERP | Google Angular | IBM Lotus Notes | سیستم‌های مدیریت موجودی | Microsoft Access | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Database | پایگاه‌های داده تولیدکننده محصول | نرم‌افزار خرید | نرم‌افزار SAP | نرم‌افزار Salesforce | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار Amazon Web Services AWS | Atlassian JIRA | Deltek Costpoint | سیستم برنامه‌ریزی منابع سازمانی ERP | Google Angular | IBM Lotus Notes | سیستم‌های مدیریت موجودی | Microsoft Access | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Oracle Database | پایگاه‌های داده تولیدکننده محصول | نرم‌افزار خرید | نرم‌افزار SAP | نرم‌افزار Salesforce | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخنوری | تفکر انتقادی | گوش دادن فعال | درک مطلب | نوشتن | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | خدمات مشتری و شخصی | حمل و نقل | اقتصاد و حسابداری | زبان انگلیسی | فروش و بازاریابی | کامپیوتر و الکترونیک | مدیریت و اداره امور | تولید مواد غذایی | تولید و فرآوری | قانون و دولت | ایمنی و امنیت عمومی</t>
+          <t>ریاضیات | خدمات مشتری و شخصی | حمل و نقل | اقتصاد و حسابداری | زبان انگلیسی | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و اداره | تولید مواد غذایی | تولید و فرآوری | قانون و دولت | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک نوشتاری | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال استقرایی | حساسیت به مسئله | بیان نوشتاری | توانایی عددی | استدلال ریاضی | نظم‌دهی اطلاعات | دید دور | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | توانایی عددی | استدلال ریاضی | ترتیب‌دهی اطلاعات | بینایی دور | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | تماس با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | اهمیت تکرار وظایف مشابه | سر و کار داشتن با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای تهویه مطبوع | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامد خطا | سطح رقابت</t>
+          <t>مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | پیامد خطا | سطح رقابت</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | کارگزاران گمرک | فروشندگان دوره‌گرد، فروشندگان روزنامه و خیابانی، و کارگران مرتبط | راننده/فروشنده | کشاورزان، دامداران و سایر مدیران کشاورزی | حمل‌ونقل‌کنندگان بار | متخصصان لجستیک | تحلیلگران لجستیک | کارمندان تدارکات | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | فروشندگان خرده‌فروشی | نمایندگان فروش، عمده‌فروشی و تولیدی، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولیدی، محصولات فنی و علمی | کارگزاران فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان حمل‌ونقل، دریافت و موجودی | انبارداران و پرکنندگان سفارش | مدیران زنجیره تأمین | وزن‌کنندگان، اندازه‌گیرندگان، بررسی‌کنندگان و نمونه‌گیران، ثبت سوابق | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
+          <t>بازرسان کشاورزی | کارگزاران گمرک | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | رانندگان توزیع و فروشندگان | کشاورزان، دامداران و سایر مدیران کشاورزی | متصدیان حمل و نقل | لجستیسین‌ها | تحلیلگران لجستیک | کارمندان تدارکات | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | فروشندگان خرده‌فروشی | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان ارسال، دریافت و موجودی کالا | قفسه‌چین‌ها و پرکننده‌های سفارش | مدیران زنجیره تأمین | توزین‌کنندگان، اندازه‌گیران، کنترل‌کنندگان و نمونه‌برداران، ثبت اسناد | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Buyer | Grocery Buyer | Procurement Specialist | Purchaser | Purchasing Coordinator | Retail Buyer | Trader</t>
+          <t>خریدار | خریدار مواد غذایی | متخصص تدارکات | خریدار | هماهنگ‌کننده خرید | خریدار خرده‌فروشی | معامله‌گر</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -565,27 +565,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخنوری | یادگیری فعال | درک مطلب | ریاضیات | نظارت | نوشتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | درک مطلب | ریاضیات | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره امور | کامپیوتر و الکترونیک | اقتصاد و حسابداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک نوشتاری | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | توانایی عددی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | دید نزدیک | نظم‌دهی اطلاعات | توجه انتخابی | خلاقیت | روانی ایده‌ها | بیان نوشتاری</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | توانایی عددی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | اصالت | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>محیط داخلی، دارای تهویه مطبوع | ایمیل | مکالمات تلفنی | تماس با دیگران | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف مشابه | فشار زمانی | اهمیت دقیق یا صحیح بودن | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | سر و کار داشتن با مشتریان خارجی یا عموم مردم | نتایج کاری و خروجی‌های سایر کارگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | مکالمات تلفنی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | فشار زمانی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | پیامدهای کاری و نتایج سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | کارمندان کارگزاری | خریداران و نمایندگان خرید، محصولات کشاورزی | کارمندان پیشخوان و اجاره | کارگزاران گمرک | فروشندگان دوره‌گرد، فروشندگان روزنامه و خیابانی، و کارگران مرتبط | مدیران بازاریابی | بازرگانان آنلاین | کارمندان سفارش | کارمندان تدارکات | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | نمایندگان فروش املاک | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | نمایندگان فروش، عمده‌فروشی و تولیدی، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولیدی، محصولات فنی و علمی | کارگزاران فروش اوراق بهادار، کالاها و خدمات مالی | انبارداران و پرکنندگان سفارش</t>
+          <t>نمایندگان فروش تبلیغات | کارمندان کارگزاری | خریداران و نمایندگان خرید، محصولات کشاورزی | کارمندان باجه و اجاره | کارگزاران گمرک | فروشندگان خانه‌به‌خانه، فروشندگان روزنامه و خیابانی و کارکنان مرتبط | مدیران بازاریابی | تاجران آنلاین | کارمندان ثبت سفارش | کارمندان تدارکات | نمایندگان خرید، به جز عمده‌فروشی، خرده‌فروشی و محصولات کشاورزی | مدیران خرید | نمایندگان فروش املاک | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش، عمده‌فروشی و تولید، به جز محصولات فنی و علمی | نمایندگان فروش، عمده‌فروشی و تولید، محصولات فنی و علمی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | قفسه‌چین‌ها و پرکننده‌های سفارش</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -612,37 +612,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Buyer | Contract Administrator (Contract Admin) | Procurement Official | Procurement Specialist | Procurement and Contracting Administrator (Procurement and Contracting Admin) | Procurement and Contracting Buyer | Purchasing Administrator (Purchasing Admin) | Purchasing Agent | Purchasing and Contracts Coordinator</t>
+          <t>خریدار | مسئول امور قراردادها (Contract Admin) | مسئول تدارکات | متخصص تدارکات | مسئول تدارکات و قراردادها (Procurement and Contracting Admin) | خریدار تدارکات و قراردادها | مسئول امور خرید (Purchasing Admin) | کارگزار خرید | هماهنگ‌کننده خرید و قراردادها</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Apple AppleWorks | Assured Software JPP | CPR International GeneralCOST Estimator | CPR Visual Estimator | Choice Job Cost | نرم‌افزار مدیریت ساخت ProEst | Corel QuattroPro | نرم‌افزار حسابداری هزینه | نرم‌افزار برآورد هزینه | نرم‌افزار گزارش‌دهی پایگاه داده | نرم‌افزار پایگاه داده | Dexter + Cheney Spectrum Construction Software | FileMaker Pro | Galorath SEER-SEM | Google Ads | Google Docs | IBM Cognos Impromptu | IBM Costimater | IBM Lotus 1-2-3 | IBM Notes | نرم‌افزار IBM Power Systems | Infor ERP SyteLine | Intuit QuickBooks | سیستم‌های مدیریت موجودی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Word | NetSuite ERP | Oracle Database | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | QSM SLIM Suite | Resources Calculations Incorporated SoftCost | SAP Business Objects | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 100 Contractor | SmugMug Flickr | Softstar Costar COCOMO II | نرم‌افزار سازمانی Software AG | نرم‌افزار مرورگر وب | WinEstimator WinEst | Xactware Xactimate</t>
+          <t>Adobe Acrobat | Apple AppleWorks | Assured Software JPP | CPR International GeneralCOST Estimator | CPR Visual Estimator | Choice Job Cost | نرم‌افزار مدیریت ساخت ProEst | Corel QuattroPro | نرم‌افزار حسابداری هزینه | نرم‌افزار برآورد هزینه | نرم‌افزار گزارش‌گیری پایگاه داده | نرم‌افزار پایگاه داده | Dexter + Cheney Spectrum Construction Software | FileMaker Pro | Galorath SEER-SEM | Google Ads | Google Docs | IBM Cognos Impromptu | IBM Costimater | IBM Lotus 1-2-3 | IBM Notes | نرم‌افزار IBM Power Systems | Infor ERP SyteLine | Intuit QuickBooks | سیستم‌های مدیریت موجودی | MicroStrategy | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Visio | Microsoft Word | NetSuite ERP | Oracle Database | Oracle E-Business Suite Financials | Oracle JD Edwards EnterpriseOne | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | QSM SLIM Suite | Resources Calculations Incorporated SoftCost | SAP Business Objects | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | Sage 100 Contractor | SmugMug Flickr | Softstar Costar COCOMO II | نرم‌افزار سازمانی Software AG | نرم‌افزار مرورگر وب | WinEstimator WinEst | Xactware Xactimate</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | نوشتن | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره امور | اداری | ریاضیات | کامپیوتر و الکترونیک | اقتصاد و حسابداری</t>
+          <t>زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | اداری | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شفاهی | بیان شفاهی | بیان نوشتاری | استدلال استقرایی | استدلال قیاسی | دید نزدیک | تشخیص گفتار | نظم‌دهی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | توانایی عددی | روانی ایده‌ها | استدلال ریاضی | خلاقیت</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | توانایی عددی | روانی ایده‌ها | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای تهویه مطبوع | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | سر و کار داشتن با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف مشابه | تناوب تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | نامه‌ها و یادداشت‌های کتبی | اهمیت تکرار وظایف یکسان | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کارمندان کارگزاری | خریداران و نمایندگان خرید، محصولات کشاورزی | برآوردکنندگان هزینه | نمایندگان خدمات مشتری | کارگزاران گمرک | سرپرستان خط اول کارگران فروش غیرخرده‌فروشی | متخصصان لجستیک | تحلیلگران لجستیک | تحلیلگران مدیریت | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و تسریع | مدیران املاک، مستغلات و انجمن‌های اجتماعی | مدیران خرید | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و مسافرتی | کارگزاران فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان حمل‌ونقل، دریافت و موجودی | مدیران زنجیره تأمین | مدیران حمل‌ونقل، ذخیره‌سازی و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
+          <t>کارمندان کارگزاری | خریداران و نمایندگان خرید، محصولات کشاورزی | برآوردکنندگان هزینه | نمایندگان خدمات مشتریان | کارگزاران گمرک | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | لجستیسین‌ها | تحلیلگران لجستیک | تحلیل‌گران مدیریت | کارمندان تدارکات | کارمندان تولید، برنامه‌ریزی و هماهنگی | مدیران املاک، مستغلات و انجمن‌های اجتماعی | مدیران خرید | مدیران فروش | نمایندگان فروش خدمات، به جز تبلیغات، بیمه، خدمات مالی و سفر | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان ارسال، دریافت و موجودی کالا | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی، به جز محصولات کشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -669,37 +669,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Claims Adjuster | Claims Analyst | Claims Examiner | Claims Representative | Claims Specialist | Corporate Claims Examiner | Field Claims Adjuster | General Adjuster | Home Office Claims Specialist | Litigation Claims Representative</t>
+          <t>کارشناس تعدیل خسارت | تحلیل‌گر خسارت | کارشناس بررسی خسارت | نماینده رسیدگی به خسارت | کارشناس خسارت | کارشناس بررسی خسارت شرکتی | کارشناس میدانی تعدیل خسارت | کارشناس عمومی تعدیل خسارت | کارشناس خسارت دفتر مرکزی | نماینده دعاوی خسارت</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4n6xprt Systems StiffCalcs | نرم‌افزار ADP | ARSoftware WinSMAC | سیستم‌های مدیریت آژانس AMS 360 | Apple Safari | AutoClaims Direct DirectLink | Automatic Data Processing Autosource | Automatic Data Processing Claims Manager &amp; Dispatch | Automatic Data Processing Estimating | سیستم مدیریت تقلب و سوءاستفاده Axonwave | BCCORP Burkitt W5 | BCCORP W5 for Adjusters | نرم‌افزار بررسی صورت‌حساب | Bramerhill ClaimsTech | Bridium Claims 3 | سیستم‌های ادعای Brightwork Alyce | برنامه‌های نرم‌افزاری تجاری | CAD Zone Insurance | شبکه ارتباطات الکترونیکی CCC EZNet | CCC GuidePost Decision Support | CCC Pathways Appraisal Quality Solution | CCC Pathways Image Management Solution | CCC TL2000 Solution | CGI INSideOUT | CGI-AMS BureauLink Enterprise | CSC Automated Work Distributor AWD | CSC Colossus | CSC Fault Evaluator | Captiva InputAccel | Castek Insure3 Claims | نرم‌افزار مدیریت و اداره پردازش ادعا | Clear Technology Tranzax | نرم‌افزار تحلیل استرس صوتی کامپیوتری CVSA | Corporate Systems ClaimsPro | Covansys ClaimConnect | Datanex ClaimTrac | نرم‌افزار سیستم مدیریت اسناد | Fair Isaac Claims Advisor | Fair Isaac SmartAdvisor | First Notice Systems ClaimCapture | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hummingbird Legal Bill Review | مدیریت محتوای سازمانی Hyland OnBase | سیستم مدیریت تقلب و سوءاستفاده IBM | ISO ClaimSearch | ISO NetMap for Claims | سیستم مدیریت اسناد InSystems Calligo | Injury Sciences EDR InSight | نرم‌افزار تشخیص تقلب در ادعاهای بیمه | LexisNexis RiskWise | سیستم هدف‌گیری پیش‌بینی‌کننده Magnify | MapScenes Evidence Recorder | MapScenes Pro | نرم‌افزار کدگذاری وضعیت پزشکی | نرم‌افزار کدگذاری رویه پزشکی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Mozilla Firefox | PhotoModeler | نرم‌افزار برآورد خسارت اموال، آسیب بدنی و مسئولیت | نرم‌افزار QwikQuote | Simsol for Adjusters | StrataCare StrataWare eReview | Tropics Claims Reserve Management | Turtle Creek Software Goldenseal Architect | Visual Statement Investigator Suite | Xactware Xactimate | Zoom</t>
+          <t>4n6xprt Systems StiffCalcs | نرم‌افزار ADP | ARSoftware WinSMAC | سیستم‌های مدیریت آژانس AMS 360 | Apple Safari | AutoClaims Direct DirectLink | Automatic Data Processing Autosource | Automatic Data Processing Claims Manager &amp; Dispatch | Automatic Data Processing Estimating | سیستم مدیریت تقلب و سوءاستفاده Axonwave | BCCORP Burkitt W5 | BCCORP W5 for Adjusters | نرم‌افزار بررسی صورت‌حساب | Bramerhill ClaimsTech | Bridium Claims 3 | سیستم‌های ادعای Brightwork Alyce | برنامه‌های نرم‌افزاری تجاری | CAD Zone Insurance | شبکه ارتباطات الکترونیکی CCC EZNet | CCC GuidePost Decision Support | CCC Pathways Appraisal Quality Solution | CCC Pathways Image Management Solution | CCC TL2000 Solution | CGI INSideOUT | CGI-AMS BureauLink Enterprise | CSC Automated Work Distributor AWD | CSC Colossus | CSC Fault Evaluator | Captiva InputAccel | Castek Insure3 Claims | نرم‌افزار مدیریت و اداره پردازش ادعا | Clear Technology Tranzax | نرم‌افزار تحلیل استرس صوتی کامپیوتری CVSA | Corporate Systems ClaimsPro | Covansys ClaimConnect | Datanex ClaimTrac | نرم‌افزار سیستم مدیریت اسناد | Fair Isaac Claims Advisor | Fair Isaac SmartAdvisor | First Notice Systems ClaimCapture | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hummingbird Legal Bill Review | Hyland OnBase Enterprise Content Management | سیستم مدیریت تقلب و سوءاستفاده IBM | ISO ClaimSearch | ISO NetMap for Claims | سیستم مدیریت اسناد InSystems Calligo | Injury Sciences EDR InSight | نرم‌افزار تشخیص تقلب در ادعاهای بیمه | LexisNexis RiskWise | سیستم هدف‌گیری پیش‌بینی‌کننده Magnify | MapScenes Evidence Recorder | MapScenes Pro | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Word | Mozilla Firefox | PhotoModeler | نرم‌افزار برآورد خسارت اموال، آسیب بدنی و مسئولیت | نرم‌افزار QwikQuote | Simsol for Adjusters | StrataCare StrataWare eReview | Tropics Claims Reserve Management | Turtle Creek Software Goldenseal Architect | Visual Statement Investigator Suite | Xactware Xactimate | Zoom</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخنوری | نوشتن | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | ریاضیات | کامپیوتر و الکترونیک | قانون و دولت | مدیریت و اداره امور | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | ریاضیات | رایانه و الکترونیک | قانون و دولت | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | دید نزدیک | حساسیت به مسئله | وضوح گفتار | نظم‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | تناوب تصمیم‌گیری | تماس با دیگران | صرف زمان برای نشستن | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف مشابه | آزادی در تصمیم‌گیری | سر و کار داشتن با مشتریان خارجی یا عموم مردم | فشار زمانی | محیط داخلی، دارای تهویه مطبوع | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های حضوری با افراد و درون تیم‌ها | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | کار با یا مشارکت در یک گروه کاری یا تیم</t>
+          <t>ایمیل | مکالمات تلفنی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | ارتباط با دیگران | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | موقعیت‌های تعارض | کار با یا مشارکت در یک گروه کاری یا تیم</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | قضات حقوق اداری، داوران و مسئولان رسیدگی | ارزیابان و ممیزان املاک | داوران، میانجی‌گران و مصالحه‌گران | مدیران جبران خسارت و مزایا | متخصصان جبران خسارت، مزایا و تحلیل شغل | افسران انطباق | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتری | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان تقلب، محققان و تحلیلگران | کارمندان پردازش ادعا و خط‌مشی بیمه | نمایندگان فروش بیمه | بیمه‌گران | وکلا | منشی‌های حقوقی و دستیاران اداری | پیراپزشکان و دستیاران حقوقی | کارآگاهان خصوصی و محققان | ممیزان و جمع‌آوری‌کنندگان مالیات، و نمایندگان درآمد | ممیزان عنوان، چکیده‌نویسان و جستجوگران</t>
+          <t>حسابداران و حسابرسان | قضات حقوق اداری، داوران و مسئولان رسیدگی | ارزیابان و ممیزان املاک | داوران، میانجی‌گران و مصالحه‌گران | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | افسران انطباق | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | نمایندگان خدمات مشتریان | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان، محققان و تحلیلگران کلاهبرداری | کارمندان پردازش بیمه و بیمه‌نامه | نمایندگان فروش بیمه | بیمه‌گران | وکلا | منشی‌های حقوقی و دستیاران اداری | پارالیگال‌ها و دستیاران حقوقی | کارآگاهان و بازرسان خصوصی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Appraiser | Automobile Appraiser (Auto Appraiser) | Automobile Damage Appraiser (Auto Damage Appraiser) | Damage Appraiser | Field Appraiser | Field Inspector | Insurance Appraiser | Material Damage Appraiser | Outside Physical Damage Appraiser | Physical Damage Appraiser</t>
+          <t>ارزیاب | ارزیاب خودرو (Auto Appraiser) | ارزیاب خسارت خودرو (Auto Damage Appraiser) | ارزیاب خسارت | ارزیاب میدانی | بازرس میدانی | ارزیاب بیمه | ارزیاب خسارت مادی | ارزیاب میدانی خسارت فیزیکی | ارزیاب خسارت فیزیکی</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نوشتن | سخنوری | درک مطلب | گوش دادن فعال | تفکر انتقادی</t>
+          <t>نگارش | سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتری و شخصی | زبان انگلیسی | کامپیوتر و الکترونیک | مکانیکی | اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مکانیک | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک نوشتاری | حساسیت به مسئله | بیان نوشتاری | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | نظم‌دهی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | تماس با دیگران | سر و کار داشتن با مشتریان خارجی یا عموم مردم | تناوب تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | در وسیله نقلیه محصور یا کار با تجهیزات محصور | بحث‌های حضوری با افراد و درون تیم‌ها | محیط بیرونی، در معرض تمام شرایط آب و هوایی | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | موقعیت‌های تعارض | محیط داخلی، دارای تهویه مطبوع | اهمیت تکرار وظایف مشابه | کار با یا مشارکت در یک گروه کاری یا تیم | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری</t>
+          <t>ایمیل | مکالمات تلفنی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | فراوانی تصمیم‌گیری | فشار زمانی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای نشستن | نامه‌ها و یادداشت‌های کتبی | موقعیت‌های تعارض | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ارزیابان و ممیزان املاک | ارزیابان اموال شخصی و تجاری | تعمیرکاران بدنه خودرو و مرتبط | تکنسین‌های مهندسی خودرو | نصب‌کنندگان و تعمیرکاران شیشه خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | بازرسان هوانوردی | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | برآوردکنندگان هزینه | مجازکنندگان اعتبار، بررسی‌کنندگان و کارمندان | تعمیرکاران موتور الکتریکی، ابزار برقی و مرتبط | تعمیرکاران الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصب‌کنندگان و تعمیرکاران تجهیزات الکترونیکی، وسایل نقلیه موتوری | بازرسان، آزمایش‌کنندگان، مرتب‌کنندگان، نمونه‌گیران و وزن‌کنندگان | کارمندان پردازش ادعا و خط‌مشی بیمه | مکانیک‌های موتورسیکلت | فروشندگان قطعات | تعمیرکاران واگن ریلی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه حمل‌ونقل، تجهیزات و سیستم‌ها، به جز هوانوردی</t>
+          <t>ارزیابان و ممیزان املاک | ارزیابان اموال شخصی و تجاری | تعمیرکنندگان بدنه خودرو و موارد مرتبط | تکنسین‌های مهندسی خودرو | نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | بازرسان هوانوردی | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | برآوردکنندگان هزینه | صادرکنندگان مجوز اعتبار، بررسی‌کنندگان و کارمندان | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | کارمندان پردازش بیمه و بیمه‌نامه | مکانیک‌های موتورسیکلت | فروشندگان قطعات | تعمیرکنندگان واگن‌های ریلی | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Driver Examiner | Driver License Agent | Driver License Examiner | Examiner | License Examiner | License Registration Examiner | Licensing Analyst | Motor Vehicle Clerk | Public Service Representative (PSR) | Transportation Services Representative (TSR)</t>
+          <t>کارشناس آزمون رانندگی | متصدی صدور گواهی‌نامه رانندگی | کارشناس آزمون گواهی‌نامه رانندگی | بازرس | کارشناس صدور پروانه | کارشناس ثبت و صدور پروانه | تحلیل‌گر صدور پروانه | متصدی امور خودرو | نماینده خدمات عمومی (PSR) | نماینده خدمات حمل‌ونقل (TSR)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | سخنوری | گوش دادن فعال | نوشتن | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | کامپیوتر و الکترونیک | مدیریت و اداره امور | اداری</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | حساسیت به مسئله | نظم‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>تماس با دیگران | سر و کار داشتن با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | اهمیت دقیق یا صحیح بودن | کار با یا مشارکت در یک گروه کاری یا تیم | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف مشابه | ایمیل | صرف زمان برای نشستن | مجاورت فیزیکی | محیط داخلی، دارای تهویه مطبوع | تناوب تصمیم‌گیری | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | در وسیله نقلیه محصور یا کار با تجهیزات محصور | موقعیت‌های تعارض | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | فشار زمانی | محیط بیرونی، در معرض تمام شرایط آب و هوایی | پیامد خطا</t>
+          <t>ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | ایمیل | صرف زمان برای نشستن | نزدیکی فیزیکی | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | موقعیت‌های تعارض | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | فشار زمانی | فضای باز، در معرض تمام شرایط آب و هوایی | پیامد خطا</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | مدیران خدمات اداری | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | مدیران انطباق | بازرسان مرگ | کارمندان دادگاه، شهرداری و مجوز | کارگزاران گمرک | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان انطباق زیست‌محیطی | نمایندگان و افسران فرصت‌های برابر | بازرسان و محققان اموال دولتی | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیلگران مدیریت | پیراپزشکان و دستیاران حقوقی | کارآگاهان خصوصی و محققان | متخصصان امور نظارتی | ممیزان و جمع‌آوری‌کنندگان مالیات، و نمایندگان درآمد | ممیزان عنوان، چکیده‌نویسان و جستجوگران</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | مدیران خدمات اداری | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | مدیران انطباق | بازرسان مرگ | کارمندان دادگاه، شهرداری و مجوز | کارگزاران گمرک | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | بازرسان انطباق زیست‌محیطی | نمایندگان و افسران فرصت‌های برابر | بازرسان و محققان اموال دولتی | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | پارالیگال‌ها و دستیاران حقوقی | کارآگاهان و بازرسان خصوصی | متخصصان امور نظارتی | بازرسان و مأموران جمع‌آوری مالیات و مأموران درآمد | بازرسان اسناد، خلاصه‌نویسان و جستجوگران</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Air Permitting and Enforcement Inspector | Compliance Investigator | Enforcement Officer | Environmental Compliance Inspector | Environmental Inspector | Environmental Protection Specialist | Environmental Quality Analyst | Resource Conservation and Recovery Act Enforcement Officer (RCRA Enforcement Officer) | Toxics Program Officer | Waste Management Specialist</t>
+          <t>بازرس مجوز و اجرای مقررات هوا | بازرس انطباق | مأمور اجرای مقررات | بازرس انطباق محیط‌زیستی | بازرس محیط‌زیست | متخصص حفاظت از محیط زیست | تحلیل‌گر کیفیت محیط‌زیست | مأمور اجرای قانون حفاظت و بازیافت منابع (RCRA) | مسئول برنامه مواد سمی | کارشناس مدیریت پسماند</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نوشتن | سخنوری | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | قانون و دولت | کامپیوتر و الکترونیک | شیمی | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | قانون و دولت | رایانه و الکترونیک | شیمی | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان نوشتاری | انعطاف‌پذیری بستار | دید نزدیک | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | سرعت ادراکی | دید دور | توانایی عددی | روانی ایده‌ها | توجه انتخابی | تجسم | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | انعطاف‌پذیری بستار | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | سرعت ادراکی | بینایی دور | توانایی عددی | روانی ایده‌ها | توجه انتخابی | تجسم | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | سر و کار داشتن با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای تهویه مطبوع | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | محیط بیرونی، در معرض تمام شرایط آب و هوایی | فشار زمانی | صرف زمان برای نشستن | در وسیله نقلیه محصور یا کار با تجهیزات محصور | در معرض آلاینده‌ها | محیط داخلی، بدون تهویه مطبوع</t>
+          <t>مکالمات تلفنی | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | نامه‌ها و یادداشت‌های کتبی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | فشار زمانی | صرف زمان برای نشستن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | متخصصان احیای زمین‌های قهوه‌ای و مدیران سایت | مدیران انطباق | افسران انطباق | دانشمندان حفاظت | بازرسان ساخت‌وساز و ساختمان | تکنسین‌ها و تکنولوژیست‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | بوم‌شناسان صنعتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | مدیران امور نظارتی | متخصصان امور نظارتی | متخصصان مدیریت امنیت | متخصصان منابع آب | مهندسان آب/فاضلاب</t>
+          <t>بازرسان کشاورزی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران انطباق | افسران انطباق | دانشمندان حفاظت | بازرسان ساختمان و ساخت‌وساز | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | بوم‌شناسان صنعتی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | مدیران امور نظارتی | متخصصان امور نظارتی | متخصصان مدیریت امنیت | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Affirmative Action Officer (AA Officer) | Civil Rights Investigator | Civil Rights Representative | Complaint Investigations Officer | Equal Employment Opportunity Officer (EEO Officer) | Equal Employment Opportunity Representative (EEO Representative) | Equal Opportunity Specialist</t>
+          <t>مسئول اقدام جبرانی استخدامی (AA) | بازرس حقوق شهروندی | نماینده حقوق شهروندی | مسئول بررسی شکایات | مسئول فرصت برابر شغلی (EEO) | نماینده فرصت برابر شغلی (EEO) | کارشناس فرصت برابر</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخنوری | نوشتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>قانون و دولت | زبان انگلیسی | پرسنل و منابع انسانی | خدمات مشتری و شخصی | جامعه‌شناسی و مردم‌شناسی | مدیریت و اداره امور | اداری | آموزش و پرورش</t>
+          <t>قانون و دولت | زبان انگلیسی | پرسنل و منابع انسانی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره | اداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک نوشتاری | درک شفاهی | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | دید نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت بستار | روانی ایده‌ها</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | بحث‌های حضوری با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تماس با دیگران | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا صحیح بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای تهویه مطبوع | تناوب تصمیم‌گیری | سر و کار داشتن با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | فشار زمانی</t>
+          <t>ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ارتباط با دیگران | نامه‌ها و یادداشت‌های کتبی | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | کار با یا مشارکت در یک گروه کاری یا تیم | موقعیت‌های تعارض | فشار زمانی</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران جبران خسارت و مزایا | متخصصان جبران خسارت، مزایا و تحلیل شغل | مدیران انطباق | افسران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | دستیاران منابع انسانی، به جز حقوق و دستمزد و زمان‌بندی | مدیران منابع انسانی | متخصصان منابع انسانی | کارمندان حقوقی قضایی | متخصصان روابط کار | معلمان حقوق، پس از متوسطه | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیلگران مدیریت | متخصصان امور نظارتی | مدیران خدمات اجتماعی و اجتماعی</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران جبران خدمات و مزایا | متخصصان جبران خدمات، مزایا و تحلیل شغل | مدیران انطباق | افسران انطباق | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | متخصصان منابع انسانی | کارمندان حقوقی قضایی | متخصصان روابط کار | مدرسان حقوق، آموزش عالی | وکلا | منشی‌های حقوقی و دستیاران اداری | تحلیل‌گران مدیریت | متخصصان امور نظارتی | مدیران خدمات اجتماعی و جامعه</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Airport Operations Officer | Housing Inspector | Housing Management Representative | Housing Quality Standard Inspector (HQS Inspector) | Neighborhood Conservation Officer | Quality Assurance Specialist | Rehabilitation Construction Specialist</t>
+          <t>افسر عملیات فرودگاه | بازرس مسکن | نماینده مدیریت مسکن | بازرس استاندارد کیفیت مسکن (HQS) | مأمور حفاظت محلات | کارشناس تضمین کیفیت | کارشناس بازسازی ساختمان</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | تفکر انتقادی | سخنوری | نوشتن | درک مطلب | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز | قانون و دولت | اداری | مهندسی و فناوری | کامپیوتر و الکترونیک | طراحی | آموزش و پرورش | ریاضیات | مکانیکی</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز | قانون و دولت | اداری | مهندسی و فناوری | رایانه و الکترونیک | طراحی | آموزش و پرورش | ریاضیات | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | نظم‌دهی اطلاعات | درک شفاهی | درک نوشتاری | بیان شفاهی | دید نزدیک | تشخیص گفتار | وضوح گفتار | دید دور | انعطاف‌پذیری بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | روانی ایده‌ها | سرعت بستار | اشتراک زمانی | حفظ کردن | تشخیص رنگ بصری | توانایی عددی | استدلال ریاضی</t>
+          <t>استدلال استقرایی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بینایی دور | انعطاف‌پذیری بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | روانی ایده‌ها | سرعت بستار | تقسیم توجه | حفظ کردن | تشخیص رنگ بصری | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | تماس با دیگران | ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | سر و کار داشتن با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا صحیح بودن | تناوب تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای تهویه مطبوع | در وسیله نقلیه محصور یا کار با تجهیزات محصور | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | موقعیت‌های تعارض | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فشار زمانی | محیط بیرونی، در معرض تمام شرایط آب و هوایی | نتایج کاری و خروجی‌های سایر کارگران | نامه‌ها و یادداشت‌های کتبی | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>مکالمات تلفنی | ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعامل با مشتریان خارجی یا عموم مردم | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | موقعیت‌های تعارض | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | فضای باز، در معرض تمام شرایط آب و هوایی | پیامدهای کاری و نتایج سایر کارکنان | نامه‌ها و یادداشت‌های کتبی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان هوانوردی | متخصصان احیای زمین‌های قهوه‌ای و مدیران سایت | تکنسین‌ها و تکنولوژیست‌های مهندسی عمران | مهندسان عمران | مدیران انطباق | افسران انطباق | مدیران ساخت‌وساز | بازرسان ساخت‌وساز و ساختمان | کارگزاران گمرک | بازرسان انطباق زیست‌محیطی | مدیران تأسیسات | بازرسان و محققان آتش‌سوزی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | متخصصان امور نظارتی | متخصصان مدیریت امنیت | ممیزان عنوان، چکیده‌نویسان و جستجوگران | بازرسان وسایل نقلیه حمل‌ونقل، تجهیزات و سیستم‌ها، به جز هوانوردی</t>
+          <t>بازرسان کشاورزی | بازرسان هوانوردی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مدیران انطباق | افسران انطباق | مدیران ساخت‌وساز | بازرسان ساختمان و ساخت‌وساز | کارگزاران گمرک | بازرسان انطباق زیست‌محیطی | مدیران تسهیلات | بازرسان و محققان آتش‌نشانی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | متخصصان امور نظارتی | متخصصان مدیریت امنیت | بازرسان اسناد، خلاصه‌نویسان و جستجوگران | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Autopsy Facilities Manager | Coroner | County Coroner | Death Investigator | Forensic Pathologist | MDI (Medicolegal Death Investigator) | MLI (Medical Legal Investigator) | Medical Examiner | Medical Legal Death Investigator | Medicolegal Investigator</t>
+          <t>مدیر تأسیسات کالبدشکافی | پزشک قانونی | پزشک قانونی شهرستان | بازرس علت مرگ | متخصص آسیب‌شناسی قانونی | MDI (بازرس پزشکی‌قانونی مرگ) | MLI (بازرس پزشکی‌قانونی) | پزشک قانونی | بازرس پزشکی‌قانونی مرگ | بازرس پزشکی‌قانونی</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخنوری | درک مطلب | گوش دادن فعال | نوشتن | یادگیری فعال | نظارت | علوم | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | پزشکی و دندانپزشکی | خدمات مشتری و شخصی | قانون و دولت | مدیریت و اداره امور | زیست‌شناسی | آموزش و پرورش | اداری | ایمنی و امنیت عمومی | جامعه‌شناسی و مردم‌شناسی | کامپیوتر و الکترونیک | درمان و مشاوره | روان‌شناسی | حمل‌ونقل | پرسنل و منابع انسانی | ارتباطات و رسانه | اقتصاد و حسابداری</t>
+          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | قانون و دولت | مدیریت و اداره | زیست‌شناسی | آموزش و پرورش | اداری | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | درمان و مشاوره | روان‌شناسی | حمل و نقل | پرسنل و منابع انسانی | ارتباطات و رسانه | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | دید نزدیک | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | سرعت ادراکی | خلاقیت | مهارت دستی | ثبات دست و بازو | تجسم | دید دور | مهارت انگشت | توجه انتخابی | سرعت بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | سرعت ادراکی | اصالت | مهارت دستی | ثبات دست و بازو | تجسم | بینایی دور | مهارت انگشتان | توجه انتخابی | سرعت بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | سر و کار داشتن با مشتریان خارجی یا عموم مردم | بحث‌های حضوری با افراد و درون تیم‌ها | تماس با دیگران | در معرض بیماری یا عفونت | محیط داخلی، دارای تهویه مطبوع | در وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | در معرض آلاینده‌ها | اهمیت دقیق یا صحیح بودن | تناوب تصمیم‌گیری | مجاورت فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، بدون تهویه مطبوع | محیط بیرونی، در معرض تمام شرایط آب و هوایی | سر و کار داشتن با افراد ناخوشایند، عصبانی یا بی‌ادب | بهداشت و ایمنی سایر کارگران | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | در معرض دماهای بسیار گرم یا سرد | نتایج کاری و خروجی‌های سایر کارگران | در معرض شرایط نوری بسیار روشن یا نامناسب | پیامد خطا | موقعیت‌های تعارض | در معرض فضای کاری تنگ، موقعیت‌های نامناسب</t>
+          <t>ایمیل | مکالمات تلفنی | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | محیط داخلی، دارای کنترل شرایط محیطی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | نامه‌ها و یادداشت‌های کتبی | محیط داخلی، بدون کنترل شرایط محیطی | فضای باز، در معرض تمام شرایط آب و هوایی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | سلامت و ایمنی سایر کارکنان | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامدهای کاری و نتایج سایر کارکنان | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | پیامد خطا | موقعیت‌های تعارض | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | افسران انطباق | کارآگاهان و محققان جنایی | پزشکان طب اورژانس | تکنسین‌های علوم پزشکی قانونی | دستیاران پزشکی | متخصصان سوابق پزشکی | منشی‌های پزشکی و دستیاران اداری | مدیران پزشکی و خدمات بهداشتی | نمایندگان بیمار | پزشکان، آسیب‌شناسان | افسران شناسایی و سوابق پلیس | افسران گشت پلیس و کلانتر | پزشکان طب پیشگیری | کارآگاهان خصوصی و محققان | روان‌پزشکان | متخصصان امور نظارتی</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | تعدیل‌کنندگان، بازرسان و محققان خسارت بیمه | متخصصان پرستاری بالینی | هماهنگ‌کنندگان تحقیقات بالینی | افسران انطباق | کارآگاهان و بازرسان جنایی | پزشکان طب اورژانس | تکنسین‌های علوم قانونی | دستیاران پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | مدیران خدمات پزشکی و بهداشتی | نمایندگان بیمار | پزشکان، آسیب‌شناسان | افسران شناسایی و سوابق پلیس | ماموران گشت پلیس و کلانتر | پزشکان طب پیشگیری | کارآگاهان و بازرسان خصوصی | روان‌پزشکان | متخصصان امور نظارتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0007_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0007_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>سخن گفتن | تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ریاضیات | خدمات مشتریان و خدمات فردی | حمل‌ونقل | اقتصاد و حسابداری | زبان انگلیسی | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و امور اداری | تولید مواد غذایی | تولید و فرآوری | حقوق و مقررات دولتی | ایمنی و امنیت عمومی</t>
+          <t>ریاضیات | خدمات مشتری و شخصی | حمل و نقل | اقتصاد و حسابداری | زبان انگلیسی | فروش و بازاریابی | رایانه و الکترونیک | مدیریت و اداره | تولید مواد غذایی | تولید و فرآوری | قانون و دولت | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | کار با اعداد | استدلال ریاضی | مرتب‌سازی اطلاعات | دید دور | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار و اصالت</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | توانایی عددی | استدلال ریاضی | ترتیب‌دهی اطلاعات | بینایی دور | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | کارگزاران گمرکی | فروشندگان دوره‌گرد، روزنامه‌فروشان، دست‌فروشان و مشاغل مرتبط | رانندگان توزیع و فروش | کشاورزان، دامداران و سایر مدیران کشاورزی | متصدیان حمل‌ونقل کالا | کارشناسان لجستیک | تحلیل‌گران لجستیک | کارمندان تدارکات | کارشناسان خرید و امور قراردادها | مدیران خرید | فروشندگان خرده‌فروشی | نمایندگان فروش عمده‌فروشی و تولیدی محصولات غیرفنی و غیرعلمی | نمایندگان فروش عمده‌فروشی و تولیدی محصولات فنی و علمی | کارگزاران فروش اوراق بهادار، کالا و خدمات مالی | کارمندان ارسال، دریافت و انبارداری | چیدمان‌کنندگان کالا و آماده‌سازان سفارش | مدیران زنجیره تأمین | متصدیان توزین، سنجش، بازرسی، نمونه‌گیری و ثبت اطلاعات | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | حق‌العمل‌کاران و کارگزاران گمرکی | بازاریابان حضوری و فروشندگان خیابانی | رانندگان توزیع و فروش مویرگی | مدیران امور کشاورزی، دامپروری و شیلات | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | فروشندگان خرده‌فروشی | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان انبار، ارسال و دریافت کالا | متصدیان چیدمان و آماده‌سازی سفارش | مدیران زنجیره تامین | متصدیان توزین، سنجش، بازرسی و نمونه‌برداری ثبت اسناد | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | درک مطلب | ریاضیات | نظارت | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | درک مطلب | ریاضیات | نظارت | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>فروش و بازاریابی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | مدیریت و امور اداری | رایانه و الکترونیک | اقتصاد و حسابداری</t>
+          <t>فروش و بازاریابی | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | کار با اعداد | استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | مرتب‌سازی اطلاعات | توجه انتخابی | ابتکار و اصالت | روانی ایده‌ها | بیان کتبی</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | حساسیت به مسئله | وضوح گفتار | تشخیص گفتار | استدلال ریاضی | توانایی عددی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | اصالت | روانی ایده‌ها | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>نمایندگان فروش تبلیغات | متصدیان کارگزاری | خریداران و کارشناسان خرید محصولات کشاورزی | متصدیان باجه و کرایه کالا | کارگزاران گمرکی | فروشندگان دوره‌گرد، روزنامه‌فروشان، دست‌فروشان و مشاغل مرتبط | مدیران بازاریابی | فروشندگان اینترنتی | کارمندان ثبت سفارش | کارمندان تدارکات | کارشناسان خرید و امور قراردادها | مدیران خرید | مشاوران املاک | فروشندگان خرده‌فروشی | مدیران فروش | نمایندگان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | نمایندگان فروش عمده‌فروشی و تولیدی محصولات غیرفنی و غیرعلمی | نمایندگان فروش عمده‌فروشی و تولیدی محصولات فنی و علمی | کارگزاران فروش اوراق بهادار، کالا و خدمات مالی | چیدمان‌کنندگان کالا و آماده‌سازان سفارش</t>
+          <t>کارشناسان فروش فضاهای تبلیغاتی | کارشناسان امور اداری و معاملات کارگزاری | خریداران و کارشناسان خرید محصولات کشاورزی | متصدیان باجه و کرایه کالا و خدمات | حق‌العمل‌کاران و کارگزاران گمرکی | بازاریابان حضوری و فروشندگان خیابانی | مدیران بازاریابی | کارشناسان تجارت الکترونیک و فروشگاه‌های اینترنتی | متصدیان ثبت و پیگیری سفارش‌ها | کارمندان تدارکات و کارپردازی | کارشناسان خرید و امور قراردادها | مدیران خرید و تدارکات | مشاوران و کارشناسان فروش املاک | فروشندگان خرده‌فروشی | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش عمده و سازمانی محصولات غیرفنی | کارشناسان فروش عمده و صنعتی کالاهای فنی و علمی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | متصدیان چیدمان و آماده‌سازی سفارش</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و دفتری | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری</t>
+          <t>زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | اداری | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | کار با اعداد | روانی ایده‌ها | استدلال ریاضی | ابتکار و اصالت</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | وضوح گفتار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | توانایی عددی | روانی ایده‌ها | استدلال ریاضی | اصالت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>متصدیان کارگزاری | خریداران و کارشناسان خرید محصولات کشاورزی | برآوردکنندگان هزینه | کارشناسان خدمات مشتریان | کارگزاران گمرکی | سرپرستان رده‌اول کارکنان فروش غیرخرده‌فروشی | کارشناسان لجستیک | تحلیل‌گران لجستیک | تحلیل‌گران مدیریت و فرآیند | کارمندان تدارکات | کارمندان برنامه‌ریزی تولید و پیگیری سفارش‌ها | مدیران املاک و مجتمع‌های مسکونی | مدیران خرید | مدیران فروش | نمایندگان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارگزاران فروش اوراق بهادار، کالا و خدمات مالی | کارمندان ارسال، دریافت و انبارداری | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
+          <t>کارشناسان امور اداری و معاملات کارگزاری | خریداران و کارشناسان خرید محصولات کشاورزی | کارشناسان برآورد هزینه و مترورها | کارشناسان خدمات و پشتیبانی مشتریان | حق‌العمل‌کاران و کارگزاران گمرکی | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | کارشناسان تحلیل مدیریت و روش‌ها | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | مدیران املاک، مستغلات و مجتمع‌های مسکونی | مدیران خرید و تدارکات | مدیران فروش | کارشناسان فروش خدمات (به‌جز تبلیغات، بیمه، خدمات مالی و گردشگری) | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کارمندان انبار، ارسال و دریافت کالا | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع | خریداران عمده‌فروشی و خرده‌فروشی کالاهای غیرکشاورزی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری و دفتری | ریاضیات | رایانه و الکترونیک | حقوق و مقررات دولتی | مدیریت و امور اداری | اقتصاد و حسابداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | اداری | ریاضیات | رایانه و الکترونیک | قانون و دولت | مدیریت و اداره | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | دید نزدیک | حساسیت به مسئله | وضوح گفتار | مرتب‌سازی اطلاعات | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری بازشناسی الگو | کار با اعداد | استدلال ریاضی | توجه انتخابی | سرعت ادراک | سرعت بازشناسی الگو</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | بینایی نزدیک | حساسیت به مسئله | وضوح گفتار | ترتیب‌دهی اطلاعات | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | توانایی عددی | استدلال ریاضی | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | قضات اداری، دادرسی و مسئولان استماع دعاوی | ارزیابان و کارشناسان املاک و مستغلات | داوران، میانجی‌گران و صلح‌دهندگان | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان اعتبارسنجی و تأیید اسناد مالی | کارشناسان خدمات مشتریان | مصاحبه‌کنندگان صلاحیت‌سنجی طرح‌های دولتی | کارشناسان و بازرسان بررسی تقلب‌های مالیاتی و تخلفات | کارمندان صدور و پرداخت خسارت بیمه | نمایندگان فروش بیمه | کارشناسان ارزیابی ریسک بیمه (آندرایتر) | وکلا | مسئولان دفاتر و کارشناسان اداری حقوقی | کارشناسان حقوقی و دستیاران وکالت | کارآگاهان و بازرسان خصوصی | ممیزان، بازرسان و مأموران وصول مالیات | کارشناسان بررسی و جستجوی اسناد مالکیت</t>
+          <t>حسابداران و حسابرسان | قضات دادگاه‌های اداری، دادرسان و مأموران استماع | کارشناسان ارزیابی و ممیزی املاک و مستغلات | داوران، میانجی‌گران و صلح‌یاران | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان خدمات و پشتیبانی مشتریان | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | کارشناسان بازرسی، کشف و تحلیل تقلب | کارمندان پردازش خسارت و بیمه‌نامه‌ها | نمایندگان و کارشناسان فروش بیمه | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان و دستیاران امور حقوقی | کارآگاهان و بازرسان خصوصی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>نگارش | سخن گفتن | درک مطلب | شنیدن فعال | تفکر انتقادی</t>
+          <t>نگارش | سخن گفتن | درک مطلب | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | مکانیک | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | مکانیک | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | حساسیت به مسئله | بیان کتبی | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ارزیابان و کارشناسان املاک و مستغلات | ارزیابان اموال شخصی و شرکتی | صافکاران و تعمیرکاران بدنه خودرو | تکنسین‌های مهندسی خودرو | نصابان و تعمیرکاران شیشه خودرو | تکنسین‌ها و مکانیک‌های خدمات پس از فروش خودرو | بازرسان ایمنی پرواز و هوانوردی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | برآوردکنندگان هزینه | کارشناسان اعتبارسنجی و تأیید اسناد مالی | تعمیرکاران موتورهای الکتریکی و ابزارآلات برقی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | بازرسان، آزمون‌گران، درجه‌بندی‌کنندگان، نمونه‌برداران و متصدیان توزین | کارمندان صدور و پرداخت خسارت بیمه | مکانیک‌های موتورسیکلت | فروشندگان لوازم یدکی خودرو | تعمیرکاران واگن‌های قطار | بازرسان حمل‌ونقل | بازرسان وسایل نقلیه، تجهیزات و سامانه‌های ترابری (به‌جز هوانوردی)</t>
+          <t>کارشناسان ارزیابی و ممیزی املاک و مستغلات | کارشناسان ارزیابی اموال منقول و دارایی‌های تجاری | صافکار و نقاش خودرو | تکنسین‌های مهندسی خودرو | نصاب و تعمیرکار شیشه خودرو | مکانیک و تکنسین خدمات خودرو | بازرسان هوانوردی و فرودگاهی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | کارشناسان برآورد هزینه و مترورها | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارمندان پردازش خسارت و بیمه‌نامه‌ها | مکانیک موتورسیکلت | فروشندگان قطعات و لوازم یدکی | تعمیرکار واگن قطار | بازرسان ترابری و حمل‌ونقل | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و امور اداری | امور اداری و دفتری</t>
+          <t>قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | رایانه و الکترونیک | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | روانی ایده‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>قضات اداری، دادرسی و مسئولان استماع دعاوی | مدیران خدمات اداری و پشتیبانی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | مدیران امور انطباق و بازرسی | پزشکان قانونی و بازرسان مرگ مشکوک | کارمندان دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | کارگزاران گمرکی | مصاحبه‌کنندگان صلاحیت‌سنجی طرح‌های دولتی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | بازرسان و ممیزان اموال دولتی | دستیاران قضایی | وکلا | مسئولان دفاتر و کارشناسان اداری حقوقی | تحلیل‌گران مدیریت و فرآیند | کارشناسان حقوقی و دستیاران وکالت | کارآگاهان و بازرسان خصوصی | کارشناسان امور نظارتی و تطبیق مقررات | ممیزان، بازرسان و مأموران وصول مالیات | کارشناسان بررسی و جستجوی اسناد مالکیت</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مدیران خدمات اداری و پشتیبانی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | مدیران تطبیق و نظارت مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | حق‌العمل‌کاران و کارگزاران گمرکی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | بازرسان و ممیزان اموال دولتی | کارشناسان پژوهش و تحریر قضایی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان و دستیاران امور حقوقی | کارآگاهان و بازرسان خصوصی | کارشناسان امور رگولاتوری و انطباق مقرراتی | ممیزان، ماموران وصول و کارشناسان مالیاتی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | استراتژی‌های یادگیری | علوم پایه | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | رایانه و الکترونیک | شیمی | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | قانون و دولت | رایانه و الکترونیک | شیمی | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | انعطاف‌پذیری بازشناسی الگو | دید نزدیک | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در طبقه‌بندی | سرعت ادراک | دید دور | کار با اعداد | روانی ایده‌ها | توجه انتخابی | تجسم فضایی | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بیان کتبی | انعطاف‌پذیری بستار | بینایی نزدیک | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری دسته‌بندی | سرعت ادراکی | بینایی دور | توانایی عددی | روانی ایده‌ها | توجه انتخابی | تجسم | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | متخصصان و مدیران احیای اراضی صنعتی آلوده | مدیران امور انطباق و بازرسی | کارشناسان پایش انطباق و بازرسی مقرراتی | دانشمندان حفاظت منابع طبیعی | بازرسان ساختمان و ابنیه | تکنسین‌ها و کاردان‌های فنی مهندسی محیط زیست | مهندسان محیط زیست | کاردان‌ها و تکنسین‌های علوم محیطی و بهداشت عمومی | کارشناسان و دانشمندان علوم محیطی و بهداشت عمومی | بازرسان و ممیزان اموال دولتی | مهندسان بهداشت حرفه‌ای و ایمنی کار (به‌جز معدن) | بوم‌شناسان صنعتی | کارشناسان بهداشت حرفه‌ای و ایمنی محیط کار | تکنسین‌های بهداشت حرفه‌ای و حفاظت محیط کار | مدیران امور مقرراتی و استانداردها | کارشناسان امور نظارتی و تطبیق مقررات | کارشناسان مدیریت امنیت | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | دانشمندان حفاظت از منابع طبیعی | بازرسان ساخت‌وساز و ساختمان | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بازرسان و ممیزان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | بوم‌شناسان صنعتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | مدیران امور انطباق مقرراتی و حقوقی صنایع | کارشناسان امور رگولاتوری و انطباق مقرراتی | کارشناسان مدیریت حراست و امنیت فیزیکی | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | تفکر انتقادی | سخن گفتن | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | امور اداری و منابع انسانی | خدمات مشتریان و خدمات فردی | جامعه‌شناسی و مردم‌شناسی | مدیریت و امور اداری | امور اداری و دفتری | آموزش و تدریس</t>
+          <t>قانون و دولت | زبان انگلیسی | پرسنل و منابع انسانی | خدمات مشتری و شخصی | جامعه‌شناسی و انسان‌شناسی | مدیریت و اداره | اداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در طبقه‌بندی | انعطاف‌پذیری بازشناسی الگو | سرعت بازشناسی الگو | روانی ایده‌ها</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | استدلال قیاسی | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | سرعت بستار | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>قضات اداری، دادرسی و مسئولان استماع دعاوی | داوران، میانجی‌گران و صلح‌دهندگان | مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدارس | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران امور انطباق و بازرسی | کارشناسان پایش انطباق و بازرسی مقرراتی | مصاحبه‌کنندگان صلاحیت‌سنجی طرح‌های دولتی | کارمندان امور اداری و کارگزینی (به‌جز حقوق و دستمزد) | مدیران منابع انسانی | کارشناسان منابع انسانی | دستیاران قضایی | کارشناسان روابط کار | اساتید حقوق دانشگاه | وکلا | مسئولان دفاتر و کارشناسان اداری حقوقی | تحلیل‌گران مدیریت و فرآیند | کارشناسان امور نظارتی و تطبیق مقررات | مدیران خدمات اجتماعی و امور عام‌المنفعه</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | مدیران عامل و مدیران ارشد اجرایی | مددکاران اجتماعی کودک، خانواده و مدرسه | مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان منابع انسانی | کارشناسان پژوهش و تحریر قضایی | کارشناسان روابط کار و امور تشکل‌های کارگری | مدرسان حقوق در دانشگاه‌ها و مراکز آموزش عالی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان امور رگولاتوری و انطباق مقرراتی | مدیران خدمات اجتماعی و خدمات مردمی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز | حقوق و مقررات دولتی | امور اداری و دفتری | مهندسی و فناوری | رایانه و الکترونیک | طراحی | آموزش و تدریس | ریاضیات | مکانیک</t>
+          <t>زبان انگلیسی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | ساختمان و ساخت‌وساز | قانون و دولت | اداری | مهندسی و فناوری | رایانه و الکترونیک | طراحی | آموزش و پرورش | ریاضیات | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | تشخیص گفتار | وضوح گفتار | دید دور | انعطاف‌پذیری بازشناسی الگو | سرعت ادراک | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | تجسم فضایی | روانی ایده‌ها | سرعت بازشناسی الگو | تقسیم توجه | حفظ در حافظه | تشخیص رنگ‌ها | کار با اعداد | استدلال ریاضی</t>
+          <t>استدلال استقرایی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | بینایی دور | انعطاف‌پذیری بستار | سرعت ادراکی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | روانی ایده‌ها | سرعت بستار | تقسیم توجه | حفظ کردن | تشخیص رنگ بصری | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بازرسان کشاورزی | بازرسان ایمنی پرواز و هوانوردی | متخصصان و مدیران احیای اراضی صنعتی آلوده | کاردان‌ها و تکنسین‌های فنی مهندسی عمران | مهندسان عمران | مدیران امور انطباق و بازرسی | کارشناسان پایش انطباق و بازرسی مقرراتی | مدیران پروژه‌های ساختمانی | بازرسان ساختمان و ابنیه | کارگزاران گمرکی | بازرسان رعایت ضوابط زیست‌محیطی | مدیران تأسیسات و ابنیه | بازرسان و کارشناسان بررسی حریق | مهندسان بهداشت حرفه‌ای و ایمنی کار (به‌جز معدن) | کارشناسان بهداشت حرفه‌ای و ایمنی محیط کار | تکنسین‌های بهداشت حرفه‌ای و حفاظت محیط کار | کارشناسان امور نظارتی و تطبیق مقررات | کارشناسان مدیریت امنیت | کارشناسان بررسی و جستجوی اسناد مالکیت | بازرسان وسایل نقلیه، تجهیزات و سامانه‌های ترابری (به‌جز هوانوردی)</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | بازرسان هوانوردی و فرودگاهی | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | مدیران پروژه‌های ساختمانی | بازرسان ساخت‌وساز و ساختمان | حق‌العمل‌کاران و کارگزاران گمرکی | بازرسان رعایت ضوابط زیست‌محیطی | مدیران امور ساختمان و تأسیسات | بازرسان و کارشناسان بررسی علل حریق | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | کارشناسان امور رگولاتوری و انطباق مقرراتی | کارشناسان مدیریت حراست و امنیت فیزیکی | کارشناسان بررسی اسناد مالکیت و خلاصه‌برداری اسناد ثبتی | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | نظارت | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | نظارت | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | مدیریت و امور اداری | زیست‌شناسی | آموزش و تدریس | امور اداری و دفتری | ایمنی و امنیت عمومی | جامعه‌شناسی و مردم‌شناسی | رایانه و الکترونیک | روان‌درمانی و مشاوره | روان‌شناسی | حمل‌ونقل | امور اداری و منابع انسانی | ارتباطات و رسانه | اقتصاد و حسابداری</t>
+          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | قانون و دولت | مدیریت و اداره | زیست‌شناسی | آموزش و پرورش | اداری | ایمنی و امنیت عمومی | جامعه‌شناسی و انسان‌شناسی | رایانه و الکترونیک | درمان و مشاوره | روان‌شناسی | حمل و نقل | پرسنل و منابع انسانی | ارتباطات و رسانه | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | حساسیت به مسئله | انعطاف‌پذیری بازشناسی الگو | انعطاف‌پذیری در طبقه‌بندی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | سرعت ادراک | ابتکار و اصالت | چابکی دستی | ثبات دست و بازو | تجسم فضایی | دید دور | چابکی انگشتان | توجه انتخابی | سرعت بازشناسی الگو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | سرعت ادراکی | اصالت | مهارت دستی | ثبات دست و بازو | تجسم | بینایی دور | مهارت انگشتان | توجه انتخابی | سرعت بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>قضات اداری، دادرسی و مسئولان استماع دعاوی | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | پرستاران متخصص بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارآگاهان و بازرسان جنایی | پزشکان طب اورژانس | تکنسین‌های علوم آزمایشگاهی پزشکی قانونی | دستیاران پزشک | کارشناسان مدارک و اسناد پزشکی | مسئولان دفاتر و کارشناسان اداری پزشکی | مدیران خدمات بهداشتی و درمانی | رابطان و مددکاران امور بیماران | پزشکان آسیب‌شناس (پاتولوژیست) | کارشناسان ثبت هویت و اسناد پلیس | مأموران گشت پلیس و انتظامی | پزشکان طب کار و پیشگیری | کارآگاهان و بازرسان خصوصی | روان‌پزشکان | کارشناسان امور نظارتی و تطبیق مقررات</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | کارشناسان ارزیابی و رسیدگی به خسارت‌های بیمه‌ای | پرستاران متخصص بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارآگاهان و بازرسان جنایی | پزشکان طب اورژانس | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کمک‌پزشکان و دستیاران مطب | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | مدیران خدمات درمانی و بهداشتی | کارشناسان امور بیماران و پذیرش | پزشکان متخصص پاتولوژی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | ماموران گشت پلیس و کلانتری | متخصصان پزشکی اجتماعی و طب پیشگیری | کارآگاهان و بازرسان خصوصی | روان‌پزشکان | کارشناسان امور رگولاتوری و انطباق مقرراتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
